--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35D7328D-D5C7-42EB-A480-DEE206FBB6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B071C7-FC91-4E66-B5B8-8F5726C904D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>usual college day , completed classes went back and did other activities.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>felt tired after classes, learned python basics.</t>
   </si>
 </sst>
 </file>
@@ -1018,27 +1024,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>45</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>300</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>300</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B071C7-FC91-4E66-B5B8-8F5726C904D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018ACE34-8A15-4459-8CAA-F75F2721731F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -200,6 +200,12 @@
   </si>
   <si>
     <t>felt tired after classes, learned python basics.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>today was a good day .</t>
   </si>
 </sst>
 </file>
@@ -1071,26 +1077,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>30</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>300</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018ACE34-8A15-4459-8CAA-F75F2721731F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0044EEB7-033C-4C5F-8276-A0A67D8938AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,12 @@
   </si>
   <si>
     <t>today was a good day .</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>trying to learn  C++.</t>
   </si>
 </sst>
 </file>
@@ -1123,26 +1129,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>360</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0044EEB7-033C-4C5F-8276-A0A67D8938AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857570B7-07B2-4B53-82F4-E22D970C2F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1174,27 +1174,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>450</v>
+      </c>
+      <c r="C10" s="14">
+        <v>10</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>300</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857570B7-07B2-4B53-82F4-E22D970C2F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EF2FA7-7177-4E79-B831-CB12E891461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>trying to learn  C++.</t>
+  </si>
+  <si>
+    <t>quite lazy day for me.</t>
   </si>
 </sst>
 </file>
@@ -1221,26 +1224,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>30</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>150</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EF2FA7-7177-4E79-B831-CB12E891461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ABC239-433F-4F2B-B1EF-E7DDDF0B5DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>quite lazy day for me.</t>
+  </si>
+  <si>
+    <t>focusing on python.</t>
   </si>
 </sst>
 </file>
@@ -1270,26 +1273,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>30</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\776\CAP-776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ABC239-433F-4F2B-B1EF-E7DDDF0B5DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D1B898-0BCD-4B09-B48A-59DF32EE26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -217,7 +217,7 @@
     <t>quite lazy day for me.</t>
   </si>
   <si>
-    <t>focusing on python.</t>
+    <t>getting a bit difficulty in learning python functions.</t>
   </si>
 </sst>
 </file>
@@ -1272,15 +1272,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B12" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D12" s="14">
         <v>30</v>
@@ -1289,24 +1289,24 @@
         <v>30</v>
       </c>
       <c r="F12" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G12" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H12" s="14">
         <v>300</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>980</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>54</v>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D1B898-0BCD-4B09-B48A-59DF32EE26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80C372C-9C4A-4BB8-BAF6-866AE4FB5998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>getting a bit difficulty in learning python functions.</t>
+  </si>
+  <si>
+    <t>long tiring day .</t>
   </si>
 </sst>
 </file>
@@ -1319,26 +1322,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>30</v>
+      </c>
+      <c r="E13" s="14">
+        <v>45</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>240</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80C372C-9C4A-4BB8-BAF6-866AE4FB5998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F4EFA4-FAEC-4AB4-A190-F8A5684265D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>long tiring day .</t>
+  </si>
+  <si>
+    <t>today I learned friend function in c++.</t>
   </si>
 </sst>
 </file>
@@ -1367,27 +1370,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>10</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F4EFA4-FAEC-4AB4-A190-F8A5684265D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9682486-FE40-4DEF-853F-10F9B7096C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>today I learned friend function in c++.</t>
+  </si>
+  <si>
+    <t>nothing much today</t>
   </si>
 </sst>
 </file>
@@ -1417,26 +1420,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>10</v>
+      </c>
+      <c r="D15" s="14">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9682486-FE40-4DEF-853F-10F9B7096C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E187CCC-A239-474F-84FF-B176830165B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>nothing much today</t>
+  </si>
+  <si>
+    <t>getting confused in coding logics.</t>
   </si>
 </sst>
 </file>
@@ -1465,27 +1468,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B16" s="14">
+        <v>360</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>30</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>100</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>240</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E187CCC-A239-474F-84FF-B176830165B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9D10CA-B906-4DF8-9A1A-845A9C5DD101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>getting confused in coding logics.</t>
+  </si>
+  <si>
+    <t>learning c++ basics.</t>
   </si>
 </sst>
 </file>
@@ -1515,26 +1518,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>240</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9D10CA-B906-4DF8-9A1A-845A9C5DD101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85468631-CC82-4088-9582-6ACE0EFF5054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t>learning c++ basics.</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>practised cisco topologies.</t>
   </si>
 </sst>
 </file>
@@ -1564,26 +1573,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>350</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>240</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85468631-CC82-4088-9582-6ACE0EFF5054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F06648F-3DF5-4737-A82F-D9D36F20042C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>practised cisco topologies.</t>
+  </si>
+  <si>
+    <t>studied for CA .</t>
   </si>
 </sst>
 </file>
@@ -1619,26 +1622,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>15</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>420</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F06648F-3DF5-4737-A82F-D9D36F20042C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1383465-0A54-4932-A7E0-ADF2A427D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1668,26 +1668,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>15</v>
+      </c>
+      <c r="D20" s="14">
+        <v>240</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>180</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1383465-0A54-4932-A7E0-ADF2A427D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653624E5-1DFA-49C6-9995-2991357C01D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1714,26 +1714,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>60</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>240</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653624E5-1DFA-49C6-9995-2991357C01D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17913FF5-49AE-4E18-A7A1-C34A7F002784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>studied for CA .</t>
+  </si>
+  <si>
+    <t>nothing much today, practised c++.</t>
   </si>
 </sst>
 </file>
@@ -1759,27 +1762,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>240</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17913FF5-49AE-4E18-A7A1-C34A7F002784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F99582-4B87-462D-829D-383BB9F411C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>nothing much today, practised c++.</t>
+  </si>
+  <si>
+    <t>preparing for dbms ca.</t>
   </si>
 </sst>
 </file>
@@ -1809,26 +1812,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>240</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F99582-4B87-462D-829D-383BB9F411C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DDE7FF-69A7-4F12-A4B2-C69DB261708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>preparing for dbms ca.</t>
+  </si>
+  <si>
+    <t>enjoyed at fresher's party, studied for dbms ca.</t>
   </si>
 </sst>
 </file>
@@ -1857,27 +1860,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>150</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3</v>
+      </c>
+      <c r="H24" s="14">
+        <v>420</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DDE7FF-69A7-4F12-A4B2-C69DB261708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389CD3EB-6E92-40B8-AB1F-A0E8E6B0E9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>enjoyed at fresher's party, studied for dbms ca.</t>
+  </si>
+  <si>
+    <t>nothing much due to fever.</t>
   </si>
 </sst>
 </file>
@@ -1907,26 +1910,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>240</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12609800.xlsx
+++ b/12609800.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A V N I S H\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389CD3EB-6E92-40B8-AB1F-A0E8E6B0E9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8566D4D-5C6E-41CD-B3C5-24ABB36924D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>nothing much due to fever.</t>
+  </si>
+  <si>
+    <t>studying for ca.</t>
   </si>
 </sst>
 </file>
@@ -1956,26 +1959,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
